--- a/stories/arbres/ATOM-SAN.SOM.001-06.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la maison est calme. Papa dit : Alban, c'est l'heure. Alban va dans sa chambre. Il prend son pyjama. Le pyjama est bleu. Il est doux. Alban met le pyjama. Les pieds sont chauds. Maman ouvre le lit. Alban se couche. Il pose la tête. L'oreiller sent le propre. Papa raconte une petite histoire. Alban écoute. Maman dit : c'est le dodo. Le corps a besoin de dormir. Alban ferme les yeux. Il respire doucement. C'est le soir. C'est le dodo. Alban est au lit.</t>
+          <t>Le soir, la maison est calme. Alban, c'est l'heure. Alban va dans sa chambre. Il prend son pyjama. Le pyjama est bleu. Il est doux. Alban met le pyjama. Les pieds sont chauds. Maman ouvre le lit. Alban se couche. Il pose la tête. L'oreiller sent le propre. Papa raconte une petite histoire. Alban écoute. C'est le dodo. Le corps a besoin de dormir. Alban ferme les yeux. Il respire doucement. C'est le soir. C'est le dodo. Alban est au lit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, la maison est calme.
+papa|Alban, c'est l'heure.
+narrateur|Alban va dans sa chambre. Il prend son pyjama. Le pyjama est bleu. Il est doux. Alban met le pyjama. Les pieds sont chauds. Maman ouvre le lit. Alban se couche. Il pose la tête. L'oreiller sent le propre. Papa raconte une petite histoire. Alban écoute.
+maman|C'est le dodo.
+narrateur|Le corps a besoin de dormir. Alban ferme les yeux. Il respire doucement. C'est le soir. C'est le dodo. Alban est au lit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Alban va dormir. Que met-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Alban a mis le pyjama. Il s'est couché. Le soir, c'est le dodo. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Alban dort. Le pyjama est chaud. La chambre est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-06.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Le corps a besoin de dormir. Alban ferme les yeux. Il respire doucement. C'est le soir. C'est le dodo. Alban est au lit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Alban va dormir. Que met-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Alban a mis le pyjama. Il s'est couché. Le soir, c'est le dodo. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Alban dort. Le pyjama est chaud. La chambre est calme.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.SOM.001-06.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alban met le pyjama</t>
+          <t>Le doudou gris d'Aniss</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le radiateur fait tic. Un doudou gris attend. Aniss met le pyjama bleu. Les pieds deviennent chauds. Il se couche. Soir, pyjama, dodo.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la maison est calme. Alban, c'est l'heure. Alban va dans sa chambre. Il prend son pyjama. Le pyjama est bleu. Il est doux. Alban met le pyjama. Les pieds sont chauds. Maman ouvre le lit. Alban se couche. Il pose la tête. L'oreiller sent le propre. Papa raconte une petite histoire. Alban écoute. C'est le dodo. Le corps a besoin de dormir. Alban ferme les yeux. Il respire doucement. C'est le soir. C'est le dodo. Alban est au lit.</t>
+          <t>Le radiateur fait tic, tic. C'est un tout petit bruit. Un doudou gris est sur la chaise. Il attend. Les draps sentent le propre. La fenêtre est un peu embuée. Dehors, le toit luist. Aniss vit ici, avec papa et maman. En ce moment, la chambre est calme. Aniss, c'est l'heure. L'heure du doudou ? L'heure du pyjama d'abord. Puis le dodo. Aniss prend le pyjama. Le pyjama est bleu. Il est doux. Les pieds sont froids, papa. Mets le pyjama. Les pieds seront chauds. Aniss met le pyjama. Un pied. Puis l'autre pied. Les pieds sont chauds. Bravo, Aniss. Tu as mis le pyjama. Je t'ouvre le lit. Maman ouvre le lit. Aniss se couche. Il pose la tête. L'oreiller sent le propre. Le doudou, maman ? Le voilà. Tout près. Le doudou gris vient contre lui. Je raconte une petite histoire. Papa raconte un nuage lent. Le nuage marche sur le toit. Il fait tic, lui aussi ? Non. Lui, il glisse. Aniss écoute. C'est le dodo. Le corps a besoin de dormir. C'est le soir. Pyjama, puis dodo. Oui. Bravo. Tu as fait du bon travail. Aniss ferme les yeux. Il respire doucement. Le radiateur fait encore tic. Aniss est au lit. C'est le soir. C'est le dodo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,57 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, la maison est calme.
-papa|Alban, c'est l'heure.
-narrateur|Alban va dans sa chambre. Il prend son pyjama. Le pyjama est bleu. Il est doux. Alban met le pyjama. Les pieds sont chauds. Maman ouvre le lit. Alban se couche. Il pose la tête. L'oreiller sent le propre. Papa raconte une petite histoire. Alban écoute.
+          <t>narrateur|Le radiateur fait tic, tic.
+narrateur|C'est un tout petit bruit.
+narrateur|Un doudou gris est sur la chaise.
+narrateur|Il attend.
+narrateur|Les draps sentent le propre.
+narrateur|La fenêtre est un peu embuée.
+narrateur|Dehors, le toit luist.
+narrateur|Aniss vit ici, avec papa et maman.
+narrateur|En ce moment, la chambre est calme.
+papa|Aniss, c'est l'heure.
+enfant-m|L'heure du doudou ?
+papa|L'heure du pyjama d'abord.
+papa|Puis le dodo.
+narrateur|Aniss prend le pyjama.
+narrateur|Le pyjama est bleu.
+narrateur|Il est doux.
+enfant-m|Les pieds sont froids, papa.
+papa|Mets le pyjama.
+papa|Les pieds seront chauds.
+narrateur|Aniss met le pyjama.
+narrateur|Un pied.
+narrateur|Puis l'autre pied.
+narrateur|Les pieds sont chauds.
+papa|Bravo, Aniss.
+papa|Tu as mis le pyjama.
+maman|Je t'ouvre le lit.
+narrateur|Maman ouvre le lit.
+narrateur|Aniss se couche.
+narrateur|Il pose la tête.
+narrateur|L'oreiller sent le propre.
+enfant-m|Le doudou, maman ?
+maman|Le voilà. Tout près.
+narrateur|Le doudou gris vient contre lui.
+papa|Je raconte une petite histoire.
+narrateur|Papa raconte un nuage lent.
+narrateur|Le nuage marche sur le toit.
+enfant-m|Il fait tic, lui aussi ?
+papa|Non. Lui, il glisse.
+narrateur|Aniss écoute.
 maman|C'est le dodo.
-narrateur|Le corps a besoin de dormir. Alban ferme les yeux. Il respire doucement. C'est le soir. C'est le dodo. Alban est au lit.</t>
+maman|Le corps a besoin de dormir.
+papa|C'est le soir.
+enfant-m|Pyjama, puis dodo.
+maman|Oui. Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Aniss ferme les yeux.
+narrateur|Il respire doucement.
+narrateur|Le radiateur fait encore tic.
+narrateur|Aniss est au lit.
+narrateur|C'est le soir.
+narrateur|C'est le dodo.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1344,7 +1402,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Alban va dormir. Que met-il ?</t>
+          <t>Aniss va dormir. Que met-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1558,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Alban va dormir. Que met-il ?</t>
+          <t>narrateur|Aniss va dormir.
+narrateur|Que met-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1587,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Alban a mis le pyjama. Il s'est couché. Le soir, c'est le dodo. Papa et maman sont là.</t>
+          <t>Aniss a mis le pyjama. Il s'est couché. Tu as mis le pyjama ? Oui. Le bleu. Bravo, Aniss. Le soir, c'est le dodo. Le doudou reste tout près.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,7 +1731,13 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Alban a mis le pyjama. Il s'est couché. Le soir, c'est le dodo. Papa et maman sont là.</t>
+          <t>narrateur|Aniss a mis le pyjama.
+narrateur|Il s'est couché.
+papa|Tu as mis le pyjama ?
+enfant-m|Oui. Le bleu.
+papa|Bravo, Aniss.
+maman|Le soir, c'est le dodo.
+narrateur|Le doudou reste tout près.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1700,7 +1765,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Alban dort. Le pyjama est chaud. La chambre est calme.</t>
+          <t>Tu es bien au chaud ? Oui, maman. Maman baisse le volet un peu. La fenêtre reste embuée. Papa reste un moment. Aniss respire. Le pyjama est chaud. Le radiateur fait tic, tout doux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,7 +1905,14 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Alban dort. Le pyjama est chaud. La chambre est calme.</t>
+          <t>maman|Tu es bien au chaud ?
+enfant-m|Oui, maman.
+narrateur|Maman baisse le volet un peu.
+narrateur|La fenêtre reste embuée.
+narrateur|Papa reste un moment.
+narrateur|Aniss respire.
+narrateur|Le pyjama est chaud.
+narrateur|Le radiateur fait tic, tout doux.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1868,7 +1940,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai mis le pyjama. Bravo. Tu as fait du bon travail. Le doudou veille. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2080,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai mis le pyjama.
+papa|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le doudou veille.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2144,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-06.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le radiateur fait tic, tic. C'est un tout petit bruit. Un doudou gris est sur la chaise. Il attend. Les draps sentent le propre. La fenêtre est un peu embuée. Dehors, le toit luist. Aniss vit ici, avec papa et maman. En ce moment, la chambre est calme. Aniss, c'est l'heure. L'heure du doudou ? L'heure du pyjama d'abord. Puis le dodo. Aniss prend le pyjama. Le pyjama est bleu. Il est doux. Les pieds sont froids, papa. Mets le pyjama. Les pieds seront chauds. Aniss met le pyjama. Un pied. Puis l'autre pied. Les pieds sont chauds. Bravo, Aniss. Tu as mis le pyjama. Je t'ouvre le lit. Maman ouvre le lit. Aniss se couche. Il pose la tête. L'oreiller sent le propre. Le doudou, maman ? Le voilà. Tout près. Le doudou gris vient contre lui. Je raconte une petite histoire. Papa raconte un nuage lent. Le nuage marche sur le toit. Il fait tic, lui aussi ? Non. Lui, il glisse. Aniss écoute. C'est le dodo. Le corps a besoin de dormir. C'est le soir. Pyjama, puis dodo. Oui. Bravo. Tu as fait du bon travail. Aniss ferme les yeux. Il respire doucement. Le radiateur fait encore tic. Aniss est au lit. C'est le soir. C'est le dodo.</t>
+          <t>Le radiateur fait tic, tic. C'est un tout petit bruit. Un doudou gris est sur la chaise. Il attend. Une oreille du doudou penche. Les draps sentent le propre. La fenêtre est un peu embuée. Un doigt y a dessiné un rond. Dehors, le toit luit. Une gouttière fait glou, tout loin. Aniss vit ici, avec papa et maman. En ce moment, la chambre est calme. Aniss, c'est l'heure. L'heure du doudou ? L'heure du pyjama d'abord. Puis le dodo. Aniss prend le pyjama. Le pyjama est bleu. Il est doux. Les pieds sont froids, papa. Mets le pyjama. Les pieds seront chauds. Aniss met le pyjama. Un pied. Puis l'autre pied. Les pieds sont chauds. Le tissu couvre les chevilles. Plus froid, les pieds. Ils sont au chaud, maintenant. Bravo, Aniss. Tu as mis le pyjama. Je t'ouvre le lit. Maman ouvre le lit. Aniss se couche. Il pose la tête. L'oreiller sent le propre. Le doudou, maman ? Le voilà. Tout près. Le doudou gris vient contre lui. Je raconte une petite histoire. Papa raconte un nuage lent. Le nuage marche sur le toit. Il est gris, tout rond. Il fait tic, lui aussi ? Non. Lui, il glisse. Tout doucement. Aniss écoute. C'est le dodo. Le corps a besoin de dormir. C'est le soir. Pyjama, puis dodo. Oui. Bravo. Aniss ferme les yeux. Il respire doucement. Le radiateur fait encore tic. Aniss est au lit. C'est le soir. C'est le dodo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt;, la maison est calme. Papa dit : Alban, c'est l'heure. Alban va dans sa chambre. Il prend son pyjama. Le pyjama est bleu. Il est doux. Alban met le pyjama. Les pieds sont chauds. Maman ouvre le lit. Alban se couche. Il pose la tête. L'oreiller sent le propre. Papa raconte une petite histoire. Alban écoute. Maman dit : c'est le dodo. Le corps a besoin de dormir. Alban ferme les yeux. Il respire doucement. C'est le soir. C'est le dodo. Alban est au lit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le radiateur fait tic, tic. C'est un tout petit bruit. Un doudou gris est sur la chaise. Il attend. Une oreille du doudou penche. Les draps sentent le propre. La fenêtre est un peu embuée. Un doigt y a dessiné un rond. Dehors, le toit luit. Une gouttière fait glou, tout loin. Aniss vit ici, avec papa et maman. En ce moment, la chambre est calme. Aniss, c'est l'heure. L'heure du doudou ? L'heure du pyjama d'abord. Puis le dodo. Aniss prend le pyjama. Le pyjama est bleu. Il est doux. Les pieds sont froids, papa. Mets le pyjama. Les pieds seront chauds. Aniss met le pyjama. Un pied. Puis l'autre pied. Les pieds sont chauds. Le tissu couvre les chevilles. Plus froid, les pieds. Ils sont au chaud, maintenant. Bravo, Aniss. Tu as mis le pyjama. Je t'ouvre le lit. Maman ouvre le lit. Aniss se couche. Il pose la tête. L'oreiller sent le propre. Le doudou, maman ? Le voilà. Tout près. Le doudou gris vient contre lui. Je raconte une petite histoire. Papa raconte un nuage lent. Le nuage marche sur le toit. Il est gris, tout rond. Il fait tic, lui aussi ? Non. Lui, il glisse. Tout doucement. Aniss écoute. C'est le dodo. Le corps a besoin de dormir. C'est le soir. Pyjama, puis dodo. Oui. Bravo. Aniss ferme les yeux. Il respire doucement. Le radiateur fait encore tic. Aniss est au lit. C'est le soir. C'est le dodo.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1328,9 +1328,12 @@
 narrateur|C'est un tout petit bruit.
 narrateur|Un doudou gris est sur la chaise.
 narrateur|Il attend.
+narrateur|Une oreille du doudou penche.
 narrateur|Les draps sentent le propre.
 narrateur|La fenêtre est un peu embuée.
-narrateur|Dehors, le toit luist.
+narrateur|Un doigt y a dessiné un rond.
+narrateur|Dehors, le toit luit.
+narrateur|Une gouttière fait glou, tout loin.
 narrateur|Aniss vit ici, avec papa et maman.
 narrateur|En ce moment, la chambre est calme.
 papa|Aniss, c'est l'heure.
@@ -1347,6 +1350,9 @@
 narrateur|Un pied.
 narrateur|Puis l'autre pied.
 narrateur|Les pieds sont chauds.
+narrateur|Le tissu couvre les chevilles.
+enfant-m|Plus froid, les pieds.
+papa|Ils sont au chaud, maintenant.
 papa|Bravo, Aniss.
 papa|Tu as mis le pyjama.
 maman|Je t'ouvre le lit.
@@ -1360,15 +1366,16 @@
 papa|Je raconte une petite histoire.
 narrateur|Papa raconte un nuage lent.
 narrateur|Le nuage marche sur le toit.
+narrateur|Il est gris, tout rond.
 enfant-m|Il fait tic, lui aussi ?
 papa|Non. Lui, il glisse.
+papa|Tout doucement.
 narrateur|Aniss écoute.
 maman|C'est le dodo.
 maman|Le corps a besoin de dormir.
 papa|C'est le soir.
 enfant-m|Pyjama, puis dodo.
 maman|Oui. Bravo.
-maman|Tu as fait du bon travail.
 narrateur|Aniss ferme les yeux.
 narrateur|Il respire doucement.
 narrateur|Le radiateur fait encore tic.
@@ -1377,7 +1384,6 @@
 narrateur|C'est le dodo.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1407,7 +1413,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Alban va dormir. Que met-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss va dormir. Que met-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1562,7 +1568,6 @@
 narrateur|Que met-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1592,7 +1597,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Alban a mis le pyjama. Il s'est couché. Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt;, c'est le dodo. Papa et maman sont là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a mis le pyjama. Il s'est couché. Tu as mis le pyjama ? Oui. Le bleu. Bravo, Aniss. Le soir, c'est le dodo. Le doudou reste tout près.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1740,7 +1745,6 @@
 narrateur|Le doudou reste tout près.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1765,12 +1769,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tu es bien au chaud ? Oui, maman. Maman baisse le volet un peu. La fenêtre reste embuée. Papa reste un moment. Aniss respire. Le pyjama est chaud. Le radiateur fait tic, tout doux.</t>
+          <t>Tu es bien au chaud ? Oui, maman. Maman baisse le volet un peu. La fenêtre reste embuée. Le rond du doigt est encore là. Papa reste un moment. Aniss respire. Le pyjama est chaud. Le radiateur fait tic, tout doux. Le doudou est bien là ? Oui. Tout près.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Alban dort. Le &lt;emphasis level="moderate"&gt;pyjama&lt;/emphasis&gt; est chaud. La chambre est calme.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Tu es bien au chaud ? Oui, maman. Maman baisse le volet un peu. La fenêtre reste embuée. Le rond du doigt est encore là. Papa reste un moment. Aniss respire. Le pyjama est chaud. Le radiateur fait tic, tout doux. Le doudou est bien là ? Oui. Tout près.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1909,13 +1913,15 @@
 enfant-m|Oui, maman.
 narrateur|Maman baisse le volet un peu.
 narrateur|La fenêtre reste embuée.
+narrateur|Le rond du doigt est encore là.
 narrateur|Papa reste un moment.
 narrateur|Aniss respire.
 narrateur|Le pyjama est chaud.
-narrateur|Le radiateur fait tic, tout doux.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+narrateur|Le radiateur fait tic, tout doux.
+papa|Le doudou est bien là ?
+enfant-m|Oui. Tout près.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1940,12 +1946,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai mis le pyjama. Bravo. Tu as fait du bon travail. Le doudou veille. L'histoire est finie.</t>
+          <t>J'ai mis le pyjama. Bravo. Le doudou veille.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai mis le pyjama. Bravo. Le doudou veille.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2082,12 +2088,9 @@
         <is>
           <t>enfant-m|J'ai mis le pyjama.
 papa|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le doudou veille.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le doudou veille.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2106,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2151,6 +2154,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-06.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-06.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alban, papa, maman</t>
+          <t>Aniss, papa, maman</t>
         </is>
       </c>
     </row>
